--- a/measurements/34/Filled_2D_sections/coronal/week34_coronal_Batch_Allmarks.xlsx
+++ b/measurements/34/Filled_2D_sections/coronal/week34_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,79 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.849791790600833</v>
+        <v>2992.176870748299</v>
       </c>
       <c r="D2" t="n">
-        <v>18.03053338353227</v>
+        <v>352.0246993927728</v>
       </c>
       <c r="E2" t="n">
-        <v>13.0902578830719</v>
+        <v>255.5717015266418</v>
       </c>
       <c r="F2" t="n">
-        <v>1.377400930110709</v>
+        <v>1.377400930110708</v>
       </c>
       <c r="G2" t="n">
         <v>0.3034246453356383</v>
       </c>
       <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.564360119047619</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.65215773809524</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.513516865079364</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.7619092987804879</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.006573932926829</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8842416158536586</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>19.65215773809524</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14.87537202380952</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="X2" t="n">
+        <v>7.53720238095238</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.167410714285714</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.564360119047619</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.314732142857143</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.559523809523809</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.663533610945866</v>
+      <c r="AK2" s="2" t="n">
+        <v>2921.179138321995</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +699,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.907792980368828</v>
+        <v>3014.285714285714</v>
       </c>
       <c r="D3" t="n">
-        <v>16.98838890180355</v>
+        <v>331.6780690352122</v>
       </c>
       <c r="E3" t="n">
-        <v>13.10454534321297</v>
+        <v>255.850647177015</v>
       </c>
       <c r="F3" t="n">
         <v>1.296373773898389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3443188241583495</v>
+        <v>0.3443188241583496</v>
       </c>
       <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.599702380952381</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.96577380952381</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.811857413419913</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.7385670731707318</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.9714176829268293</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8549923780487805</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>18.96577380952381</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14.41964285714286</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.134672619047619</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.119047619047619</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.0234375</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.599702380952381</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.193824404761905</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.544642857142857</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>18.57312600307348</v>
+      <c r="AK3" s="2" t="n">
+        <v>362.6181743457204</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +782,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.852766210588936</v>
+        <v>2993.310657596372</v>
       </c>
       <c r="D4" t="n">
-        <v>17.46537302761543</v>
+        <v>340.9906162534441</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96065525892304</v>
+        <v>253.0413645789737</v>
       </c>
       <c r="F4" t="n">
         <v>1.347568674476626</v>
@@ -619,24 +801,60 @@
         <v>0.3235018737250626</v>
       </c>
       <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5234375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.28497023809524</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.877637987012988</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7161775914634146</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.936547256097561</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8263624237804879</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>18.28497023809524</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13.98251488095238</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.932291666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7.427455357142857</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.071614583333333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.5234375</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.911086309523809</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.420014880952381</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.79749443283895</v>
+      <c r="AK4" s="2" t="n">
+        <v>249.8558436887605</v>
       </c>
     </row>
     <row r="5">
@@ -647,43 +865,76 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.836406900654373</v>
+        <v>2987.074829931973</v>
       </c>
       <c r="D5" t="n">
-        <v>19.00572251692051</v>
+        <v>371.0641062827337</v>
       </c>
       <c r="E5" t="n">
-        <v>12.95228581893735</v>
+        <v>252.877961226872</v>
       </c>
       <c r="F5" t="n">
-        <v>1.467364354261896</v>
+        <v>1.467364354261895</v>
       </c>
       <c r="G5" t="n">
-        <v>0.272620226217214</v>
+        <v>0.2726202262172141</v>
       </c>
       <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.72023809523809</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.9823795995671</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.6771150914634146</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9588414634146342</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8533727134146342</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>18.72023809523809</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18.04315476190476</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13.21986607142857</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6.452752976190476</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.779761904761905</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.910023384353742</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>1.451448328111829</v>
+      <c r="AK5" s="2" t="n">
+        <v>1.451448328111828</v>
       </c>
     </row>
     <row r="6">
@@ -694,42 +945,75 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.991374182034503</v>
+        <v>3046.145124716553</v>
       </c>
       <c r="D6" t="n">
-        <v>18.64303819144644</v>
+        <v>363.9831265949068</v>
       </c>
       <c r="E6" t="n">
-        <v>12.99514822552844</v>
+        <v>253.7147986888885</v>
       </c>
       <c r="F6" t="n">
         <v>1.434615278556266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2889335354505293</v>
+        <v>0.2889335354505292</v>
       </c>
       <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.199776785714286</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.50074404761905</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.124751984126984</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.6841653963414634</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9475990853658537</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.8435912093495935</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>18.50074404761905</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17.55208333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>13.35751488095238</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.9375</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.199776785714286</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.764880952380952</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.26864769345238</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.2817080965786912</v>
       </c>
     </row>
@@ -741,43 +1025,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.994348602022606</v>
+        <v>3047.278911564626</v>
       </c>
       <c r="D7" t="n">
-        <v>18.33505240591561</v>
+        <v>357.9700707821619</v>
       </c>
       <c r="E7" t="n">
-        <v>13.11291473086287</v>
+        <v>256.0140495073227</v>
       </c>
       <c r="F7" t="n">
         <v>1.398243852128603</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2988330552223603</v>
+        <v>0.2988330552223604</v>
       </c>
       <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.584821428571428</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.09077380952381</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.950520833333333</v>
+      </c>
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.719798018292683</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8753810975609756</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8182164634146342</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>17.09077380952381</v>
+      </c>
+      <c r="N7" t="n">
+        <v>16.78013392857143</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14.0531994047619</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.119047619047619</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.584821428571428</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.743675595238095</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.2</v>
+      <c r="AK7" s="2" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1105,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.977394408090423</v>
+        <v>3040.816326530612</v>
       </c>
       <c r="D8" t="n">
-        <v>19.24269151687622</v>
+        <v>375.6906439009167</v>
       </c>
       <c r="E8" t="n">
-        <v>13.10107860914091</v>
+        <v>255.7829633213225</v>
       </c>
       <c r="F8" t="n">
         <v>1.46878681450321</v>
@@ -807,24 +1124,63 @@
         <v>0.2707318139464292</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5522103658536586</v>
+        <v>1.592261904761905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9315929878048781</v>
+        <v>18.18824404761905</v>
       </c>
       <c r="K8" t="n">
-        <v>0.707102705792683</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>7.023302218614718</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18.18824404761905</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14.34709821428571</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10.78125</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6.785714285714286</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.592261904761905</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.537202380952381</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.192708333333333</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6454315929878049</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.683221726190476</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1191,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.000297441998811</v>
+        <v>3049.546485260771</v>
       </c>
       <c r="D9" t="n">
-        <v>18.82979070849535</v>
+        <v>367.6292471658616</v>
       </c>
       <c r="E9" t="n">
-        <v>13.19128553460284</v>
+        <v>257.5441461517697</v>
       </c>
       <c r="F9" t="n">
         <v>1.427441674209978</v>
@@ -854,24 +1210,63 @@
         <v>0.2835469708788295</v>
       </c>
       <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.569940476190476</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.66071428571428</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.959550865800867</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.7533346036585367</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.9557926829268293</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8368267276422765</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>18.66071428571428</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15.64546130952381</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14.70796130952381</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.751116071428571</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.86235119047619</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.566592261904762</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.569940476190476</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.745535714285714</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.072172619047619</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.9267387576219512</v>
+      <c r="AK9" s="2" t="n">
+        <v>18.09347098214285</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1277,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.902141582391434</v>
+        <v>3012.131519274376</v>
       </c>
       <c r="D10" t="n">
-        <v>21.15307934109758</v>
+        <v>412.9886918976193</v>
       </c>
       <c r="E10" t="n">
-        <v>13.03310799889448</v>
+        <v>254.4559180736542</v>
       </c>
       <c r="F10" t="n">
         <v>1.623026475564529</v>
@@ -901,24 +1296,60 @@
         <v>0.2219256364097428</v>
       </c>
       <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.356770833333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.72395833333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.66538525132275</v>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.6342416158536586</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.959032012195122</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7797256097560976</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>12.3828125</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>18.72395833333333</v>
+      </c>
+      <c r="R10" t="n">
+        <v>15.22321428571428</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9.561011904761905</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.652529761904762</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.144345238095238</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.356770833333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7926924542682927</v>
+      <c r="AK10" s="2" t="n">
+        <v>7.314303422994828</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1360,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.963414634146342</v>
+        <v>3035.487528344671</v>
       </c>
       <c r="D11" t="n">
-        <v>19.94683924244671</v>
+        <v>389.4382899715787</v>
       </c>
       <c r="E11" t="n">
-        <v>13.01882051258552</v>
+        <v>254.176971912384</v>
       </c>
       <c r="F11" t="n">
         <v>1.532154101300018</v>
@@ -948,16 +1379,60 @@
         <v>0.2515133360860353</v>
       </c>
       <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.66443452380952</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.186011904761905</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.6186166158536586</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9559832317073171</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.7720322027439025</v>
+      <c r="P11" t="n">
+        <v>12.07775297619048</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18.66443452380952</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15.07300967261905</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8.214285714285714</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.879836309523809</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.898065476190476</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.868489583333333</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.15</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1443,79 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.002379535990482</v>
+        <v>3050.340136054422</v>
       </c>
       <c r="D12" t="n">
-        <v>19.2594303096213</v>
+        <v>376.0174489021301</v>
       </c>
       <c r="E12" t="n">
-        <v>13.03310795237378</v>
+        <v>254.4559171653929</v>
       </c>
       <c r="F12" t="n">
         <v>1.477731204253049</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2711078769012725</v>
+        <v>0.2711078769012726</v>
       </c>
       <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.484375</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.61049107142857</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.707031250000002</v>
+      </c>
+      <c r="L12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.6099466463414634</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.9532202743902439</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7672923018292683</v>
+      <c r="P12" t="n">
+        <v>11.90848214285714</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>18.61049107142857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>14.98046875</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.164806547619047</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.043898809523809</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.484375</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.095238095238095</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.234933035714286</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>18.03345556972789</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1526,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.957168352171327</v>
+        <v>3033.106575963719</v>
       </c>
       <c r="D13" t="n">
-        <v>18.34097049875957</v>
+        <v>358.0856144995916</v>
       </c>
       <c r="E13" t="n">
-        <v>13.0414773807293</v>
+        <v>254.6193202904292</v>
       </c>
       <c r="F13" t="n">
         <v>1.406356807846099</v>
@@ -1026,16 +1545,60 @@
         <v>0.2972513160276649</v>
       </c>
       <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.042410714285714</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.38541666666666</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.707093253968251</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.5922256097560976</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.9416920731707318</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7829014227642276</v>
+      <c r="M13" t="n">
+        <v>18.38541666666666</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15.90773809523809</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11.5625</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7.565104166666666</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.376860119047619</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.042410714285714</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.562127976190476</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.891555059523809</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>15.390625</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1609,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.803390838786437</v>
+        <v>2974.489795918367</v>
       </c>
       <c r="D14" t="n">
-        <v>18.24586084121611</v>
+        <v>356.2287116618383</v>
       </c>
       <c r="E14" t="n">
-        <v>12.88575113110426</v>
+        <v>251.5789506548927</v>
       </c>
       <c r="F14" t="n">
         <v>1.41597184794089</v>
@@ -1065,16 +1628,63 @@
         <v>0.2945537166460793</v>
       </c>
       <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.358630952380952</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.36160714285714</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.492373511904761</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.572313262195122</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.8380335365853658</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7430767276422765</v>
+      <c r="M14" t="n">
+        <v>16.36160714285714</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.98772321428571</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11.17373511904762</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.110863095238095</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7.563244047619047</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.904947916666666</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.7734375</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.648809523809524</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.358630952380952</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>12.46482683982684</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1695,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.697501487209994</v>
+        <v>2934.126984126984</v>
       </c>
       <c r="D15" t="n">
-        <v>18.54691319058581</v>
+        <v>362.1064003876277</v>
       </c>
       <c r="E15" t="n">
-        <v>12.8773816998412</v>
+        <v>251.41554747309</v>
       </c>
       <c r="F15" t="n">
         <v>1.440270516390341</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2812006802982517</v>
+        <v>0.2812006802982518</v>
       </c>
       <c r="H15" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16.79315476190476</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.166700487012986</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5750762195121951</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8601371951219513</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7526994410569107</v>
+      <c r="M15" t="n">
+        <v>16.79315476190476</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16.06584821428571</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11.22767857142857</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.900669642857143</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.793898809523809</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.914713541666667</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.500744047619047</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.772042410714286</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>12.12642609126984</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1781,82 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.547888161808448</v>
+        <v>2877.097505668934</v>
       </c>
       <c r="D16" t="n">
-        <v>18.00440979003906</v>
+        <v>351.514667329334</v>
       </c>
       <c r="E16" t="n">
-        <v>12.86901230928374</v>
+        <v>251.252145086016</v>
       </c>
       <c r="F16" t="n">
         <v>1.399051407935217</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2926021697475202</v>
+        <v>0.2926021697475203</v>
       </c>
       <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.321428571428571</v>
+      </c>
+      <c r="J16" t="n">
+        <v>18.19196428571428</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.461867559523808</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.6177591463414634</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.9317835365853658</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.7894435975609756</v>
+      <c r="M16" t="n">
+        <v>18.19196428571428</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15.98586309523809</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.0610119047619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.646205357142857</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6.488095238095238</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.769345238095238</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.321428571428571</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.847842261904762</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.619047619047619</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>18.23350694444444</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1867,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.463414634146342</v>
+        <v>2844.897959183673</v>
       </c>
       <c r="D17" t="n">
-        <v>19.44618286446827</v>
+        <v>379.6635702110472</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76654863939053</v>
+        <v>249.2516639119103</v>
       </c>
       <c r="F17" t="n">
         <v>1.523213784222627</v>
@@ -1182,16 +1886,60 @@
         <v>0.2480154312721657</v>
       </c>
       <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.117931547619047</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16.76897321428571</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.218783820346321</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.6350990853658537</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8588986280487805</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7837509527439025</v>
+      <c r="P17" t="n">
+        <v>12.39955357142857</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16.76897321428571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>15.30180431547619</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5.03720238095238</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.697916666666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.117931547619047</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.790178571428571</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.892857142857143</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>15.35923549107143</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1950,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.325996430696015</v>
+        <v>2792.517006802721</v>
       </c>
       <c r="D18" t="n">
-        <v>19.49006065508215</v>
+        <v>380.520231837318</v>
       </c>
       <c r="E18" t="n">
-        <v>12.68327512392184</v>
+        <v>247.6258476575215</v>
       </c>
       <c r="F18" t="n">
         <v>1.536674121207233</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2423539962755931</v>
+        <v>0.2423539962755932</v>
       </c>
       <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.813616071428571</v>
+      </c>
+      <c r="J18" t="n">
+        <v>18.46354166666666</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9.531715029761903</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6088986280487805</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.9456935975609756</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8113090701219513</v>
+      <c r="P18" t="n">
+        <v>11.88802083333333</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>18.46354166666666</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15.83984375</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5.318080357142857</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.98735119047619</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.775297619047619</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.813616071428571</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2030,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.20464009518144</v>
+        <v>2746.25850340136</v>
       </c>
       <c r="D19" t="n">
-        <v>20.16461807053264</v>
+        <v>393.6901623294467</v>
       </c>
       <c r="E19" t="n">
-        <v>12.68572648269374</v>
+        <v>247.6737075192588</v>
       </c>
       <c r="F19" t="n">
         <v>1.589551697968723</v>
@@ -1260,16 +2049,57 @@
         <v>0.2226599737048659</v>
       </c>
       <c r="H19" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.253720238095238</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18.16964285714286</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8.287450396825397</v>
+      </c>
+      <c r="L19" t="n">
         <v>4</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6198551829268293</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.930640243902439</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8060451600609757</v>
+      <c r="P19" t="n">
+        <v>12.10193452380952</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>18.16964285714286</v>
+      </c>
+      <c r="R19" t="n">
+        <v>15.73707217261905</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.253720238095238</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.652529761904762</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.951264880952381</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>6.859537760416666</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2110,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.519928613920285</v>
+        <v>2485.260770975056</v>
       </c>
       <c r="D20" t="n">
-        <v>16.16055663911308</v>
+        <v>315.5156296207791</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30110329825704</v>
+        <v>220.6405882040659</v>
       </c>
       <c r="F20" t="n">
         <v>1.429998134925951</v>
@@ -1299,16 +2129,57 @@
         <v>0.3137184592375168</v>
       </c>
       <c r="H20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="J20" t="n">
+        <v>17.92038690476191</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.875826719576719</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6087080792682927</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.9178734756097562</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.7282774390243903</v>
+      <c r="M20" t="n">
+        <v>17.92038690476191</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.8515625</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11.88430059523809</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8.638392857142856</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.117559523809524</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.434027777777778</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2190,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.472635336109459</v>
+        <v>2467.233560090703</v>
       </c>
       <c r="D21" t="n">
-        <v>16.163007965902</v>
+        <v>315.5634888580867</v>
       </c>
       <c r="E21" t="n">
-        <v>11.24640472342328</v>
+        <v>219.5726636477879</v>
       </c>
       <c r="F21" t="n">
-        <v>1.437171110536217</v>
+        <v>1.437171110536218</v>
       </c>
       <c r="G21" t="n">
         <v>0.3113483940327038</v>
       </c>
       <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16.75223214285714</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.742311507936508</v>
+      </c>
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.6126143292682927</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.8580411585365854</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7125889227642276</v>
+      <c r="M21" t="n">
+        <v>16.75223214285714</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.02455357142857</v>
+      </c>
+      <c r="O21" t="n">
+        <v>11.96056547619048</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8.597470238095237</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.29985119047619</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.069196428571428</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>4.357886904761905</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2269,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.079706101190476</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2291,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>7.580450148809523</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2308,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>5.764671688988095</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>2.71391369047619</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.593625992063492</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>2.086123511904761</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.596200980392157</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.15235469187675</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.360491462209884</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/34/Filled_2D_sections/coronal/week34_coronal_Batch_Allmarks.xlsx
+++ b/measurements/34/Filled_2D_sections/coronal/week34_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2427,4 +2633,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week34_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2921.179138321996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>176.2365212886258</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2467.233560090703</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3050.340136054422</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>362.6181743457204</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24.55747631240395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>315.5156296207791</v>
+      </c>
+      <c r="F11" t="n">
+        <v>412.9886918976193</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.451448328111829</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.07931354595037145</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.296373773898389</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.623026475564529</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2817080965786913</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03235311363008298</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2219256364097428</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3443188241583496</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>11</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.105012502906165</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6708203932499369</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.268027892769755</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.380312702938989</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>63</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15.45510912698413</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.447985606278319</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11.17373511904762</v>
+      </c>
+      <c r="F48" t="n">
+        <v>19.65215773809524</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.932988221884496</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.691312275589439</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.697916666666667</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.78125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>94</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.386315064589665</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6049031976478436</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.117931547619047</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.779761904761905</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>